--- a/artfynd/A 18648-2023 artfynd.xlsx
+++ b/artfynd/A 18648-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 18648-2023 artfynd.xlsx
+++ b/artfynd/A 18648-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -812,6 +812,134 @@
       <c r="AY2" t="inlineStr">
         <is>
           <t>BFiV utflykt Skinnskatteberg 2020-08-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>120538542</v>
+      </c>
+      <c r="B3" t="n">
+        <v>106467</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>245</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Skogsklocka</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Campanula cervicaria</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Vätterskoga, vid avtaget in på gamla tippen (skogsklocka), Vstm</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>539708</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6629246</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Skinnskatteberg</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Skinnskatteberg</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>U-Ski-0206</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2024-06-29</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2024-06-29</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF3" t="inlineStr"/>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Leif Johansson</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Leif Johansson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
         </is>
       </c>
     </row>

--- a/artfynd/A 18648-2023 artfynd.xlsx
+++ b/artfynd/A 18648-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -812,134 +812,6 @@
       <c r="AY2" t="inlineStr">
         <is>
           <t>BFiV utflykt Skinnskatteberg 2020-08-29</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="n">
-        <v>120538542</v>
-      </c>
-      <c r="B3" t="n">
-        <v>106594</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E3" t="n">
-        <v>245</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Skogsklocka</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>Campanula cervicaria</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>blomknopp</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>Vätterskoga, vid avtaget in på gamla tippen (skogsklocka), Vstm</t>
-        </is>
-      </c>
-      <c r="Q3" t="n">
-        <v>539708</v>
-      </c>
-      <c r="R3" t="n">
-        <v>6629246</v>
-      </c>
-      <c r="S3" t="n">
-        <v>10</v>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>Västmanland</t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>Skinnskatteberg</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>Västmanland</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>Skinnskatteberg</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>U-Ski-0206</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>2024-06-29</t>
-        </is>
-      </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t>2024-06-29</t>
-        </is>
-      </c>
-      <c r="AD3" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE3" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF3" t="inlineStr"/>
-      <c r="AG3" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT3" t="inlineStr"/>
-      <c r="AW3" t="inlineStr">
-        <is>
-          <t>Leif Johansson</t>
-        </is>
-      </c>
-      <c r="AX3" t="inlineStr">
-        <is>
-          <t>Leif Johansson</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr">
-        <is>
-          <t>Floraväkteri Sverige</t>
         </is>
       </c>
     </row>
